--- a/Excel/GiftPackEquipConfig.xlsx
+++ b/Excel/GiftPackEquipConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="15">
   <si>
     <t>#</t>
   </si>
@@ -66,6 +66,12 @@
   </si>
   <si>
     <t>新手武器</t>
+  </si>
+  <si>
+    <t>1002,1003</t>
+  </si>
+  <si>
+    <t>新手衣服</t>
   </si>
 </sst>
 </file>
@@ -1182,7 +1188,30 @@
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:10">
-      <c r="D7" s="3"/>
+      <c r="C7" s="1">
+        <v>2</v>
+      </c>
+      <c r="D7" s="6">
+        <v>200002</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="3">
+        <v>5</v>
+      </c>
+      <c r="I7" s="3">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="8" customHeight="1" spans="1:10">
       <c r="D8" s="3"/>
